--- a/docs/4/db-automation/Учебный_план_Управление_и_автоматизация_баз_данных.xlsx
+++ b/docs/4/db-automation/Учебный_план_Управление_и_автоматизация_баз_данных.xlsx
@@ -174,7 +174,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
@@ -195,16 +195,16 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Управление и автоматизация БД»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Администратор БД отвечает за доступ, сохранность и скорость работы данных. Разбираются зоны ответственности, регламентные задачи и границы автоматизации.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Управление и автоматизация БД</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="45" customHeight="1">
+          <t xml:space="preserve">администратор БД, регламент, обслуживание, доступность, зона ответственности</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
@@ -225,12 +225,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Установка SQLite/клиент»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студенты устанавливают SQLite и клиент, создают учебную базу и подключаются к ней из командной строки. Сдают файл базы и протокол проверки подключения.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Установка SQLite/клиент</t>
+          <t xml:space="preserve">файл базы, подключение, командная строка, версия, порт</t>
         </is>
       </c>
     </row>
@@ -255,16 +255,16 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Архитектура СУБД»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">СУБД делится на процессы, память и файлы на диске, и от этой раскладки зависит поведение запросов. Разбираются клиент-серверная и файловая модели.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Архитектура СУБД</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="45" customHeight="1">
+          <t xml:space="preserve">ядро, клиент-сервер, буферный кэш, журнал, файл данных, процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
@@ -285,16 +285,16 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Пользователи и роли»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студенты создают пользователей учебной базы, выдают права через роли и проверяют доступ от каждого аккаунта. Сдают SQL-скрипт с ролями и таблицу проверки прав.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пользователи и роли</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="45" customHeight="1">
+          <t xml:space="preserve">привилегия, GRANT, REVOKE, минимальные привилегии, учётная запись, проверка доступа</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
@@ -315,12 +315,12 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Установка и настройка»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Настройка СУБД сводится к нескольким параметрам: расположение файлов, память, журнал и сетевой доступ. Разбирается, что менять и как проверить результат.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Установка и настройка</t>
+          <t xml:space="preserve">конфигурация, параметр, кэш, журнал, порт, перезапуск</t>
         </is>
       </c>
     </row>
@@ -345,16 +345,16 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Пользователи и роли»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Доступ к данным строится на ролях, а не на отдельных аккаунтах. Разбираются привилегии, владение объектами и проверка выданных прав.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пользователи и роли</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
+          <t xml:space="preserve">привилегия, владелец объекта, схема, GRANT, аудит прав, наследование ролей</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">7-8</t>
@@ -375,12 +375,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Резервное копирование; Восстановление.</t>
+          <t xml:space="preserve">Студенты делают полную и инкрементную копию учебной базы и восстанавливают её на чистом месте. Сдают скрипты копирования и протокол восстановления с проверкой данных.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Резервное копирование, Восстановление</t>
+          <t xml:space="preserve">полная копия, инкремент, точка восстановления, проверка данных, протокол, чистое место</t>
         </is>
       </c>
     </row>
@@ -405,16 +405,16 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Резервное копирование»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Копия нужна не для отчёта, а для восстановления в срок. Разбираются виды копий, расписание, хранение и проверка пригодности копии к восстановлению.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Резервное копирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1">
+          <t xml:space="preserve">полная копия, дифференциальная копия, инкремент, расписание, хранение, проверка копии</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
@@ -435,16 +435,16 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Восстановление»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Восстановление возвращает базу к нужному моменту, а не просто к последней копии. Разбираются полное и точечное восстановление и порядок применения журналов.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Восстановление</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
+          <t xml:space="preserve">журнал, целостность, точка отказа, порядок применения, проверка данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">11-12</t>
@@ -465,12 +465,12 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Индексы; Оптимизация запроса.</t>
+          <t xml:space="preserve">Студенты добавляют индексы к учебной базе и сравнивают планы запросов до и после. Сдают SQL-скрипты индексов и замеры времени выполнения.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Индексы, Оптимизация запроса</t>
+          <t xml:space="preserve">план запроса, полное сканирование, селективность, время выполнения, замер, составной ключ</t>
         </is>
       </c>
     </row>
@@ -495,16 +495,16 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Репликация»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Репликация держит копии базы на нескольких узлах и распределяет чтение. Разбираются ведущий и ведомый узлы, отставание и конфликты записи.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Репликация</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="45" customHeight="1">
+          <t xml:space="preserve">ведущий узел, ведомый узел, отставание, конфликт записи, журнал изменений, переключение</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
@@ -525,16 +525,16 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Транзакции»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студенты проверяют свойства транзакций на учебной базе: фиксацию, откат и изоляцию параллельных изменений. Сдают SQL-скрипты сценариев и таблицу наблюдений.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Транзакции</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="45" customHeight="1">
+          <t xml:space="preserve">фиксация, откат, уровень изоляции, параллельная сессия, ACID, блокировка</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
@@ -555,12 +555,12 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Индексы и производительность»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Индекс ускоряет чтение и замедляет запись, поэтому его строят под конкретный запрос. Разбираются виды индексов, селективность и цена поддержки.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Индексы и производительность</t>
+          <t xml:space="preserve">B-дерево, порядок столбцов, селективность, покрытие запроса, стоимость записи, статистика</t>
         </is>
       </c>
     </row>
@@ -585,12 +585,12 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Импорт JSON»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студенты загружают данные из JSON в таблицы учебной базы и проверяют результат запросами. Сдают скрипт импорта и отчёт о числе загруженных строк.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Импорт JSON</t>
+          <t xml:space="preserve">разбор структуры, тип данных, проверка строк, скрипт, кодировка, связь таблиц</t>
         </is>
       </c>
     </row>
@@ -615,12 +615,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Оптимизация запросов»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Медленный запрос обычно вызван лишним сканированием, плохим соединением или недостатком статистики. Разбирается чтение плана и порядок исправления.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оптимизация запросов</t>
+          <t xml:space="preserve">план выполнения, соединение, сканирование, статистика, подзапрос, время отклика</t>
         </is>
       </c>
     </row>
@@ -645,16 +645,16 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Экспорт»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студенты выгружают данные учебной базы в файл для обмена и проверяют выгрузку обратной загрузкой. Сдают скрипт экспорта и отчёт о сверке строк.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Экспорт</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="45" customHeight="1">
+          <t xml:space="preserve">формат обмена, CSV, кодировка, сверка, выборка, файл</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
@@ -675,12 +675,12 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Транзакции и блокировки»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Транзакции удерживают данные согласованными, а блокировки решают, кто и когда меняет строку. Разбираются уровни изоляции, взаимные блокировки и откат.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Транзакции и блокировки</t>
+          <t xml:space="preserve">уровень изоляции, взаимная блокировка, ожидание, откат, долгая транзакция, фиксация</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Скрипт автоматизации»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студенты пишут скрипт, который создаёт таблицы, загружает данные и делает копию без ручных шагов. Сдают скрипт с проверкой запуска на чистой базе.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Скрипт автоматизации</t>
+          <t xml:space="preserve">идемпотентность, схема, загрузка данных, повторный запуск, проверка, командный файл</t>
         </is>
       </c>
     </row>
@@ -735,16 +735,16 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Импорт и экспорт»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Обмен данными требует договорённости о формате, кодировке и правилах ошибок. Разбираются CSV и JSON, пакетная загрузка и проверка целостности.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Импорт и экспорт</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="45" customHeight="1">
+          <t xml:space="preserve">CSV, JSON, кодировка, пакетная загрузка, ошибка строки, целостность</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">22</t>
@@ -765,16 +765,16 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Автоматизация скриптов»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Автоматизация убирает ручные шаги из обслуживания базы и делает их повторяемыми. Разбираются параметры скрипта, журналирование и безопасный повторный запуск.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Автоматизация скриптов</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
+          <t xml:space="preserve">параметр, журнал, код возврата, повторный запуск, обработка ошибок, расписание</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">23-24</t>
@@ -795,12 +795,12 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Планировщик; Мониторинг.</t>
+          <t xml:space="preserve">Студенты ставят скрипт обслуживания в планировщик и настраивают сбор метрик учебной базы. Сдают задание планировщика, скрипт метрик и отчёт наблюдений.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Планировщик, Мониторинг</t>
+          <t xml:space="preserve">расписание, метрика, журнал запуска, соединение, наблюдение, порог</t>
         </is>
       </c>
     </row>
@@ -825,16 +825,16 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Планировщик заданий»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Планировщик запускает обслуживание базы без участия человека. Разбираются расписание, права запуска, журнал и обработка сбоя задания.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Планировщик заданий</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="45" customHeight="1">
+          <t xml:space="preserve">расписание, задание, права запуска, журнал, сбой, учётная запись службы</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">26</t>
@@ -855,16 +855,16 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Мониторинг»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Мониторинг отвечает, что с базой сейчас и что изменится через неделю. Разбираются метрики, пороги оповещений и разбор инцидента по данным наблюдения.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мониторинг</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
+          <t xml:space="preserve">метрика, порог, оповещение, журнал, нагрузка, инцидент</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">27-28</t>
@@ -885,16 +885,16 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Аудит; Безопасность.</t>
+          <t xml:space="preserve">Студенты включают аудит действий в учебной базе и проверяют защиту доступа, секретов и копий. Сдают настройки аудита, выгрузку событий и список рисков.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Аудит, Безопасность</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
+          <t xml:space="preserve">событие, журнал доступа, секрет, права, риск, мера защиты</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="45" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">29</t>
@@ -915,12 +915,12 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Аудит»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Аудит фиксирует, кто и что сделал с данными, и помогает разобрать инцидент. Разбираются события, хранение журнала и разграничение доступа к нему.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Аудит</t>
+          <t xml:space="preserve">событие, журнал, политика, хранение, разбор инцидента, подотчётность</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Миграция»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студенты переносят учебную базу на новую версию схемы с сохранением данных. Сдают скрипты миграции и отката и отчёт о проверке данных.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Миграция</t>
+          <t xml:space="preserve">версия схемы, откат, перенос данных, проверка, скрипт, совместимость</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Безопасность»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Безопасность базы строится на минимальных правах, защите секретов и контроле доступа к копиям. Разбираются типовые атаки и меры защиты данных.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Безопасность</t>
+          <t xml:space="preserve">привилегия, строка подключения, секрет, шифрование, инъекция, доступ к копиям</t>
         </is>
       </c>
     </row>
@@ -1005,16 +1005,16 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Итоговая БД»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студенты собирают учебную базу целиком: схема, роли, индексы, копия и скрипт обслуживания. Сдают базу и комплект скриптов с протоколом проверки.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Итоговая БД</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
+          <t xml:space="preserve">схема, ограничение, роль, индекс, копия, чек-лист</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="45" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">33</t>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Миграции»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Миграция меняет схему на работающей базе без остановки и потери данных. Разбираются версии, прямой и обратный скрипт, проверка и порядок выпуска.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Миграции</t>
+          <t xml:space="preserve">версия, обратный скрипт, совместимость, проверка, выпуск, окно обслуживания</t>
         </is>
       </c>
     </row>

--- a/docs/4/db-automation/Учебный_план_Управление_и_автоматизация_баз_данных.xlsx
+++ b/docs/4/db-automation/Учебный_план_Управление_и_автоматизация_баз_данных.xlsx
@@ -160,7 +160,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Минуты</t>
+          <t xml:space="preserve">Часы</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -191,7 +191,7 @@
         </is>
       </c>
       <c r="D6" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -221,7 +221,7 @@
         </is>
       </c>
       <c r="D7" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -251,7 +251,7 @@
         </is>
       </c>
       <c r="D8" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -281,7 +281,7 @@
         </is>
       </c>
       <c r="D9" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -311,7 +311,7 @@
         </is>
       </c>
       <c r="D10" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -341,7 +341,7 @@
         </is>
       </c>
       <c r="D11" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -371,7 +371,7 @@
         </is>
       </c>
       <c r="D12" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="D13" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -431,7 +431,7 @@
         </is>
       </c>
       <c r="D14" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="D15" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="D16" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="D17" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="D18" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="D19" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D20" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="D21" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D22" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="D23" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="D24" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="D25" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="D26" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="D27" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="D28" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="D29" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="D31" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="D32" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="D33" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="D34" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="D35" s="6">
-        <v>2970</v>
+        <v>66</v>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>

--- a/docs/4/db-automation/Учебный_план_Управление_и_автоматизация_баз_данных.xlsx
+++ b/docs/4/db-automation/Учебный_план_Управление_и_автоматизация_баз_данных.xlsx
@@ -212,12 +212,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 1. Установка SQLite/клиент</t>
+          <t xml:space="preserve">Лекция 2. Архитектура PostgreSQL</t>
         </is>
       </c>
       <c r="D7" s="6">
@@ -225,16 +225,16 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты устанавливают SQLite и клиент, создают учебную базу и подключаются к ней из командной строки. Сдают файл базы и протокол проверки подключения.</t>
+          <t xml:space="preserve">PostgreSQL делится на процессы, разделяемую память и файлы WAL; от этой раскладки зависит поведение запросов. Разбираются клиент-серверная и файловая модели.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">файл базы, подключение, командная строка, версия, порт</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="45" customHeight="1">
+          <t xml:space="preserve">ядро, клиент-сервер, буферный кэш, журнал, файл данных, процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
@@ -247,7 +247,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 2. Архитектура СУБД</t>
+          <t xml:space="preserve">Лекция 3. Установка и настройка PostgreSQL</t>
         </is>
       </c>
       <c r="D8" s="6">
@@ -255,12 +255,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">СУБД делится на процессы, память и файлы на диске, и от этой раскладки зависит поведение запросов. Разбираются клиент-серверная и файловая модели.</t>
+          <t xml:space="preserve">Настройка PostgreSQL сводится к расположению файлов, памяти, WAL и сетевому доступу. Разбирается, что менять и как проверить результат после перезапуска.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ядро, клиент-сервер, буферный кэш, журнал, файл данных, процесс</t>
+          <t xml:space="preserve">конфигурация, параметр, кэш, журнал, порт, перезапуск</t>
         </is>
       </c>
     </row>
@@ -277,117 +277,117 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Практика 1. Установка PostgreSQL и подключение</t>
+        </is>
+      </c>
+      <c r="D9" s="6">
+        <v>2</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Студенты устанавливают PostgreSQL в учебной Linux VM, создают учебную базу и подключаются к ней через psql. Сдают протокол установки, список баз и проверку подключения.</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PostgreSQL, VirtualBox, psql, createdb, подключение, порт 5432</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 4. Пользователи и роли</t>
+        </is>
+      </c>
+      <c r="D10" s="6">
+        <v>2</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Доступ к данным строится на ролях, а не на отдельных аккаунтах. Разбираются привилегии, владение объектами и проверка выданных прав.</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">привилегия, владелец объекта, схема, GRANT, аудит прав, наследование ролей</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Практика 2. Пользователи и роли</t>
         </is>
       </c>
-      <c r="D9" s="6">
-        <v>2</v>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="D11" s="6">
+        <v>2</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Студенты создают пользователей учебной базы, выдают права через роли и проверяют доступ от каждого аккаунта. Сдают SQL-скрипт с ролями и таблицу проверки прав.</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">привилегия, GRANT, REVOKE, минимальные привилегии, учётная запись, проверка доступа</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 3. Установка и настройка</t>
-        </is>
-      </c>
-      <c r="D10" s="6">
-        <v>2</v>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Настройка СУБД сводится к нескольким параметрам: расположение файлов, память, журнал и сетевой доступ. Разбирается, что менять и как проверить результат.</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">конфигурация, параметр, кэш, журнал, порт, перезапуск</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 4. Пользователи и роли</t>
-        </is>
-      </c>
-      <c r="D11" s="6">
-        <v>2</v>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Доступ к данным строится на ролях, а не на отдельных аккаунтах. Разбираются привилегии, владение объектами и проверка выданных прав.</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">привилегия, владелец объекта, схема, GRANT, аудит прав, наследование ролей</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12" ht="45" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 3. Резервное копирование; Восстановление</t>
+          <t xml:space="preserve">Лекция 5. Резервное копирование</t>
         </is>
       </c>
       <c r="D12" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты делают полную и инкрементную копию учебной базы и восстанавливают её на чистом месте. Сдают скрипты копирования и протокол восстановления с проверкой данных.</t>
+          <t xml:space="preserve">Копия нужна не для отчёта, а для восстановления в срок. Разбираются виды копий, расписание, хранение и проверка пригодности копии к восстановлению.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">полная копия, инкремент, точка восстановления, проверка данных, протокол, чистое место</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
+          <t xml:space="preserve">полная копия, дифференциальная копия, инкремент, расписание, хранение, проверка копии</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -397,7 +397,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 5. Резервное копирование</t>
+          <t xml:space="preserve">Лекция 6. Восстановление</t>
         </is>
       </c>
       <c r="D13" s="6">
@@ -405,119 +405,119 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Копия нужна не для отчёта, а для восстановления в срок. Разбираются виды копий, расписание, хранение и проверка пригодности копии к восстановлению.</t>
+          <t xml:space="preserve">Восстановление возвращает базу к нужному моменту, а не просто к последней копии. Разбираются полное и точечное восстановление и порядок применения журналов.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">полная копия, дифференциальная копия, инкремент, расписание, хранение, проверка копии</t>
+          <t xml:space="preserve">журнал, целостность, точка отказа, порядок применения, проверка данных</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">9-10</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 6. Восстановление</t>
+          <t xml:space="preserve">Практика 3. Резервное копирование; Восстановление</t>
         </is>
       </c>
       <c r="D14" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Восстановление возвращает базу к нужному моменту, а не просто к последней копии. Разбираются полное и точечное восстановление и порядок применения журналов.</t>
+          <t xml:space="preserve">Студенты делают полную и инкрементную копию учебной базы и восстанавливают её на чистом месте. Сдают скрипты копирования и протокол восстановления с проверкой данных.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">журнал, целостность, точка отказа, порядок применения, проверка данных</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
+          <t xml:space="preserve">полная копия, инкремент, точка восстановления, проверка данных, протокол, чистое место</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">11-12</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 4. Индексы; Оптимизация запроса</t>
+          <t xml:space="preserve">Лекция 7. Репликация</t>
         </is>
       </c>
       <c r="D15" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты добавляют индексы к учебной базе и сравнивают планы запросов до и после. Сдают SQL-скрипты индексов и замеры времени выполнения.</t>
+          <t xml:space="preserve">Репликация держит копии базы на нескольких узлах и распределяет чтение. Разбираются ведущий и ведомый узлы, отставание и конфликты записи.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">план запроса, полное сканирование, селективность, время выполнения, замер, составной ключ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="45" customHeight="1">
+          <t xml:space="preserve">ведущий узел, ведомый узел, отставание, конфликт записи, журнал изменений, переключение</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 8. Индексы и производительность</t>
+        </is>
+      </c>
+      <c r="D16" s="6">
+        <v>2</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Индекс ускоряет чтение и замедляет запись, поэтому его строят под конкретный запрос. Разбираются виды индексов, селективность и цена поддержки.</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B-дерево, порядок столбцов, селективность, покрытие запроса, стоимость записи, статистика</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 7. Репликация</t>
-        </is>
-      </c>
-      <c r="D16" s="6">
-        <v>2</v>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Репликация держит копии базы на нескольких узлах и распределяет чтение. Разбираются ведущий и ведомый узлы, отставание и конфликты записи.</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ведущий узел, ведомый узел, отставание, конфликт записи, журнал изменений, переключение</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14</t>
-        </is>
-      </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 5. Транзакции</t>
+          <t xml:space="preserve">Лекция 9. Оптимизация запросов</t>
         </is>
       </c>
       <c r="D17" s="6">
@@ -525,46 +525,46 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты проверяют свойства транзакций на учебной базе: фиксацию, откат и изоляцию параллельных изменений. Сдают SQL-скрипты сценариев и таблицу наблюдений.</t>
+          <t xml:space="preserve">Медленный запрос обычно вызван лишним сканированием, плохим соединением или недостатком статистики. Разбирается чтение плана и порядок исправления.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">фиксация, откат, уровень изоляции, параллельная сессия, ACID, блокировка</t>
+          <t xml:space="preserve">план выполнения, соединение, сканирование, статистика, подзапрос, время отклика</t>
         </is>
       </c>
     </row>
     <row r="18" ht="60" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">14-15</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 8. Индексы и производительность</t>
+          <t xml:space="preserve">Практика 4. Индексы; Оптимизация запроса</t>
         </is>
       </c>
       <c r="D18" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Индекс ускоряет чтение и замедляет запись, поэтому его строят под конкретный запрос. Разбираются виды индексов, селективность и цена поддержки.</t>
+          <t xml:space="preserve">Студенты добавляют индексы к учебной базе и сравнивают планы запросов до и после. Сдают SQL-скрипты индексов и замеры времени выполнения.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">B-дерево, порядок столбцов, селективность, покрытие запроса, стоимость записи, статистика</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="45" customHeight="1">
+          <t xml:space="preserve">план запроса, полное сканирование, селективность, время выполнения, замер, составной ключ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
@@ -572,12 +572,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 6. Импорт JSON</t>
+          <t xml:space="preserve">Лекция 10. Транзакции и блокировки</t>
         </is>
       </c>
       <c r="D19" s="6">
@@ -585,16 +585,16 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты загружают данные из JSON в таблицы учебной базы и проверяют результат запросами. Сдают скрипт импорта и отчёт о числе загруженных строк.</t>
+          <t xml:space="preserve">Транзакции удерживают данные согласованными, а блокировки решают, кто и когда меняет строку. Разбираются уровни изоляции, взаимные блокировки и откат.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">разбор структуры, тип данных, проверка строк, скрипт, кодировка, связь таблиц</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customHeight="1">
+          <t xml:space="preserve">уровень изоляции, взаимная блокировка, ожидание, откат, долгая транзакция, фиксация</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
@@ -602,12 +602,12 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 9. Оптимизация запросов</t>
+          <t xml:space="preserve">Практика 5. Транзакции</t>
         </is>
       </c>
       <c r="D20" s="6">
@@ -615,12 +615,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Медленный запрос обычно вызван лишним сканированием, плохим соединением или недостатком статистики. Разбирается чтение плана и порядок исправления.</t>
+          <t xml:space="preserve">Студенты проверяют свойства транзакций на учебной базе: фиксацию, откат и изоляцию параллельных изменений. Сдают SQL-скрипты сценариев и таблицу наблюдений.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">план выполнения, соединение, сканирование, статистика, подзапрос, время отклика</t>
+          <t xml:space="preserve">фиксация, откат, уровень изоляции, параллельная сессия, ACID, блокировка</t>
         </is>
       </c>
     </row>
@@ -632,12 +632,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 7. Экспорт</t>
+          <t xml:space="preserve">Лекция 11. Импорт и экспорт</t>
         </is>
       </c>
       <c r="D21" s="6">
@@ -645,16 +645,16 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты выгружают данные учебной базы в файл для обмена и проверяют выгрузку обратной загрузкой. Сдают скрипт экспорта и отчёт о сверке строк.</t>
+          <t xml:space="preserve">Обмен данными требует договорённости о формате, кодировке и правилах ошибок. Разбираются CSV и JSON, пакетная загрузка и проверка целостности.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">формат обмена, CSV, кодировка, сверка, выборка, файл</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="60" customHeight="1">
+          <t xml:space="preserve">CSV, JSON, кодировка, пакетная загрузка, ошибка строки, целостность</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
@@ -662,12 +662,12 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 10. Транзакции и блокировки</t>
+          <t xml:space="preserve">Практика 6. Импорт JSON</t>
         </is>
       </c>
       <c r="D22" s="6">
@@ -675,12 +675,12 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Транзакции удерживают данные согласованными, а блокировки решают, кто и когда меняет строку. Разбираются уровни изоляции, взаимные блокировки и откат.</t>
+          <t xml:space="preserve">Студенты загружают данные из JSON в таблицы учебной базы и проверяют результат запросами. Сдают скрипт импорта и отчёт о числе загруженных строк.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">уровень изоляции, взаимная блокировка, ожидание, откат, долгая транзакция, фиксация</t>
+          <t xml:space="preserve">разбор структуры, тип данных, проверка строк, скрипт, кодировка, связь таблиц</t>
         </is>
       </c>
     </row>
@@ -697,117 +697,117 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Практика 7. Экспорт</t>
+        </is>
+      </c>
+      <c r="D23" s="6">
+        <v>2</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Студенты выгружают данные учебной базы в файл для обмена и проверяют выгрузку обратной загрузкой. Сдают скрипт экспорта и отчёт о сверке строк.</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">формат обмена, CSV, кодировка, сверка, выборка, файл</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 12. Автоматизация скриптов</t>
+        </is>
+      </c>
+      <c r="D24" s="6">
+        <v>2</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Автоматизация убирает ручные шаги из обслуживания базы и делает их повторяемыми. Разбираются параметры скрипта, журналирование и безопасный повторный запуск.</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">параметр, журнал, код возврата, повторный запуск, обработка ошибок, расписание</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="45" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Практика 8. Скрипт автоматизации</t>
         </is>
       </c>
-      <c r="D23" s="6">
-        <v>2</v>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="D25" s="6">
+        <v>2</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Студенты пишут скрипт, который создаёт таблицы, загружает данные и делает копию без ручных шагов. Сдают скрипт с проверкой запуска на чистой базе.</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">идемпотентность, схема, загрузка данных, повторный запуск, проверка, командный файл</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="45" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 11. Импорт и экспорт</t>
-        </is>
-      </c>
-      <c r="D24" s="6">
-        <v>2</v>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Обмен данными требует договорённости о формате, кодировке и правилах ошибок. Разбираются CSV и JSON, пакетная загрузка и проверка целостности.</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CSV, JSON, кодировка, пакетная загрузка, ошибка строки, целостность</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 12. Автоматизация скриптов</t>
-        </is>
-      </c>
-      <c r="D25" s="6">
-        <v>2</v>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Автоматизация убирает ручные шаги из обслуживания базы и делает их повторяемыми. Разбираются параметры скрипта, журналирование и безопасный повторный запуск.</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">параметр, журнал, код возврата, повторный запуск, обработка ошибок, расписание</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="60" customHeight="1">
+    <row r="26" ht="45" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-24</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 9. Планировщик; Мониторинг</t>
+          <t xml:space="preserve">Лекция 13. Планировщик заданий</t>
         </is>
       </c>
       <c r="D26" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты ставят скрипт обслуживания в планировщик и настраивают сбор метрик учебной базы. Сдают задание планировщика, скрипт метрик и отчёт наблюдений.</t>
+          <t xml:space="preserve">Планировщик запускает обслуживание базы без участия человека. Разбираются расписание, права запуска, журнал и обработка сбоя задания.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">расписание, метрика, журнал запуска, соединение, наблюдение, порог</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="45" customHeight="1">
+          <t xml:space="preserve">расписание, задание, права запуска, журнал, сбой, учётная запись службы</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 13. Планировщик заданий</t>
+          <t xml:space="preserve">Лекция 14. Мониторинг</t>
         </is>
       </c>
       <c r="D27" s="6">
@@ -825,79 +825,79 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Планировщик запускает обслуживание базы без участия человека. Разбираются расписание, права запуска, журнал и обработка сбоя задания.</t>
+          <t xml:space="preserve">Мониторинг отвечает, что с базой сейчас и что изменится через неделю. Разбираются метрики, пороги оповещений и разбор инцидента по данным наблюдения.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">расписание, задание, права запуска, журнал, сбой, учётная запись службы</t>
+          <t xml:space="preserve">метрика, порог, оповещение, журнал, нагрузка, инцидент</t>
         </is>
       </c>
     </row>
     <row r="28" ht="60" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25-26</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 14. Мониторинг</t>
+          <t xml:space="preserve">Практика 9. Планировщик; Мониторинг</t>
         </is>
       </c>
       <c r="D28" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мониторинг отвечает, что с базой сейчас и что изменится через неделю. Разбираются метрики, пороги оповещений и разбор инцидента по данным наблюдения.</t>
+          <t xml:space="preserve">Студенты ставят скрипт обслуживания в планировщик и настраивают сбор метрик учебной базы. Сдают задание планировщика, скрипт метрик и отчёт наблюдений.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">метрика, порог, оповещение, журнал, нагрузка, инцидент</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="60" customHeight="1">
+          <t xml:space="preserve">расписание, метрика, журнал запуска, соединение, наблюдение, порог</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="45" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">27-28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 10. Аудит; Безопасность</t>
+          <t xml:space="preserve">Лекция 15. Аудит</t>
         </is>
       </c>
       <c r="D29" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты включают аудит действий в учебной базе и проверяют защиту доступа, секретов и копий. Сдают настройки аудита, выгрузку событий и список рисков.</t>
+          <t xml:space="preserve">Аудит фиксирует, кто и что сделал с данными, и помогает разобрать инцидент. Разбираются события, хранение журнала и разграничение доступа к нему.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">событие, журнал доступа, секрет, права, риск, мера защиты</t>
+          <t xml:space="preserve">событие, журнал, политика, хранение, разбор инцидента, подотчётность</t>
         </is>
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 15. Аудит</t>
+          <t xml:space="preserve">Лекция 16. Безопасность</t>
         </is>
       </c>
       <c r="D30" s="6">
@@ -915,19 +915,19 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Аудит фиксирует, кто и что сделал с данными, и помогает разобрать инцидент. Разбираются события, хранение журнала и разграничение доступа к нему.</t>
+          <t xml:space="preserve">Безопасность базы строится на минимальных правах, защите секретов и контроле доступа к копиям. Разбираются типовые атаки и меры защиты данных.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">событие, журнал, политика, хранение, разбор инцидента, подотчётность</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="45" customHeight="1">
+          <t xml:space="preserve">привилегия, строка подключения, секрет, шифрование, инъекция, доступ к копиям</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">29-30</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -937,20 +937,20 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 11. Миграция</t>
+          <t xml:space="preserve">Практика 10. Аудит; Безопасность</t>
         </is>
       </c>
       <c r="D31" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты переносят учебную базу на новую версию схемы с сохранением данных. Сдают скрипты миграции и отката и отчёт о проверке данных.</t>
+          <t xml:space="preserve">Студенты включают аудит действий в учебной базе и проверяют защиту доступа, секретов и копий. Сдают настройки аудита, выгрузку событий и список рисков.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">версия схемы, откат, перенос данных, проверка, скрипт, совместимость</t>
+          <t xml:space="preserve">событие, журнал доступа, секрет, права, риск, мера защиты</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 16. Безопасность</t>
+          <t xml:space="preserve">Лекция 17. Миграции</t>
         </is>
       </c>
       <c r="D32" s="6">
@@ -975,12 +975,12 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Безопасность базы строится на минимальных правах, защите секретов и контроле доступа к копиям. Разбираются типовые атаки и меры защиты данных.</t>
+          <t xml:space="preserve">Миграция меняет схему на работающей базе без остановки и потери данных. Разбираются версии, прямой и обратный скрипт, проверка и порядок выпуска.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">привилегия, строка подключения, секрет, шифрование, инъекция, доступ к копиям</t>
+          <t xml:space="preserve">версия, обратный скрипт, совместимость, проверка, выпуск, окно обслуживания</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 12. Итоговая БД</t>
+          <t xml:space="preserve">Практика 11. Миграция</t>
         </is>
       </c>
       <c r="D33" s="6">
@@ -1005,12 +1005,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты собирают учебную базу целиком: схема, роли, индексы, копия и скрипт обслуживания. Сдают базу и комплект скриптов с протоколом проверки.</t>
+          <t xml:space="preserve">Студенты переносят учебную базу на новую версию схемы с сохранением данных. Сдают скрипты миграции и отката и отчёт о проверке данных.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">схема, ограничение, роль, индекс, копия, чек-лист</t>
+          <t xml:space="preserve">версия схемы, откат, перенос данных, проверка, скрипт, совместимость</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 17. Миграции</t>
+          <t xml:space="preserve">Практика 12. Итоговая БД</t>
         </is>
       </c>
       <c r="D34" s="6">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Миграция меняет схему на работающей базе без остановки и потери данных. Разбираются версии, прямой и обратный скрипт, проверка и порядок выпуска.</t>
+          <t xml:space="preserve">Студенты собирают учебную базу целиком: схема, роли, индексы, копия и скрипт обслуживания. Сдают базу и комплект скриптов с протоколом проверки.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">версия, обратный скрипт, совместимость, проверка, выпуск, окно обслуживания</t>
+          <t xml:space="preserve">схема, ограничение, роль, индекс, копия, чек-лист</t>
         </is>
       </c>
     </row>

--- a/docs/4/db-automation/Учебный_план_Управление_и_автоматизация_баз_данных.xlsx
+++ b/docs/4/db-automation/Учебный_план_Управление_и_автоматизация_баз_данных.xlsx
@@ -187,7 +187,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 1. Управление и автоматизация БД</t>
+          <t xml:space="preserve">Управление и автоматизация БД</t>
         </is>
       </c>
       <c r="D6" s="6">
@@ -195,16 +195,16 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Администратор БД отвечает за доступ, сохранность и скорость работы данных. Разбираются зоны ответственности, регламентные задачи и границы автоматизации.</t>
+          <t xml:space="preserve">Администратор MySQL отвечает за доступ, сохранность и скорость данных, а автоматизация на C# убирает ручные шаги. Разбираются роли, регламент и инструменты XAMPP, Visual Studio и .NET SDK 10.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">администратор БД, регламент, обслуживание, доступность, зона ответственности</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
+          <t xml:space="preserve">администратор БД, XAMPP, MySQL, регламент, автоматизация, .NET SDK 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
@@ -217,7 +217,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 2. Архитектура PostgreSQL</t>
+          <t xml:space="preserve">Архитектура MySQL и InnoDB</t>
         </is>
       </c>
       <c r="D7" s="6">
@@ -225,12 +225,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PostgreSQL делится на процессы, разделяемую память и файлы WAL; от этой раскладки зависит поведение запросов. Разбираются клиент-серверная и файловая модели.</t>
+          <t xml:space="preserve">MySQL в XAMPP состоит из сервера, InnoDB, буферного пула и журналов. Разбирается, как устроены таблицы, транзакции и восстановление после сбоя.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ядро, клиент-сервер, буферный кэш, журнал, файл данных, процесс</t>
+          <t xml:space="preserve">MySQL, InnoDB, буферный пул, redo log, undo log, binary log</t>
         </is>
       </c>
     </row>
@@ -247,7 +247,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 3. Установка и настройка PostgreSQL</t>
+          <t xml:space="preserve">XAMPP, MySQL и подключение из .NET</t>
         </is>
       </c>
       <c r="D8" s="6">
@@ -255,16 +255,16 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Настройка PostgreSQL сводится к расположению файлов, памяти, WAL и сетевому доступу. Разбирается, что менять и как проверить результат после перезапуска.</t>
+          <t xml:space="preserve">XAMPP запускает Apache и MySQL, phpMyAdmin даёт браузерный доступ, а .NET подключается к базе через MySqlConnector. Разбирается установка, кодировка utf8mb4 и строка подключения.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">конфигурация, параметр, кэш, журнал, порт, перезапуск</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t xml:space="preserve">XAMPP, phpMyAdmin, utf8mb4, MySqlConnector, строка подключения, порт 3306</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
@@ -277,7 +277,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 1. Установка PostgreSQL и подключение</t>
+          <t xml:space="preserve">Запуск XAMPP, база utf8mb4, подключение из .NET</t>
         </is>
       </c>
       <c r="D9" s="6">
@@ -285,12 +285,12 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты устанавливают PostgreSQL в учебной Linux VM, создают учебную базу и подключаются к ней через psql. Сдают протокол установки, список баз и проверку подключения.</t>
+          <t xml:space="preserve">Запускают MySQL в XAMPP, создают базу dean в phpMyAdmin с utf8mb4, подключаются из консольного приложения .NET SDK 10 и сдают протокол.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PostgreSQL, VirtualBox, psql, createdb, подключение, порт 5432</t>
+          <t xml:space="preserve">XAMPP, phpMyAdmin, utf8mb4, MySqlConnector, .NET SDK 10, порт 3306</t>
         </is>
       </c>
     </row>
@@ -307,7 +307,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 4. Пользователи и роли</t>
+          <t xml:space="preserve">Пользователи и роли MySQL</t>
         </is>
       </c>
       <c r="D10" s="6">
@@ -315,16 +315,16 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Доступ к данным строится на ролях, а не на отдельных аккаунтах. Разбираются привилегии, владение объектами и проверка выданных прав.</t>
+          <t xml:space="preserve">Доступ к MySQL строится на пользователях, ролях и привилегиях. Разбираются GRANT, REVOKE, роли MySQL 8 и проверка прав из приложения.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">привилегия, владелец объекта, схема, GRANT, аудит прав, наследование ролей</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
+          <t xml:space="preserve">пользователь, роль, GRANT, REVOKE, привилегия, минимальные права</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="45" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
@@ -337,7 +337,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 2. Пользователи и роли</t>
+          <t xml:space="preserve">Роли и доступ в MySQL</t>
         </is>
       </c>
       <c r="D11" s="6">
@@ -345,12 +345,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты создают пользователей учебной базы, выдают права через роли и проверяют доступ от каждого аккаунта. Сдают SQL-скрипт с ролями и таблицу проверки прав.</t>
+          <t xml:space="preserve">Создают пользователей и роли MySQL, выдают минимальные права и проверяют доступ из phpMyAdmin и .NET. Сдают SQL-скрипт и матрицу прав.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">привилегия, GRANT, REVOKE, минимальные привилегии, учётная запись, проверка доступа</t>
+          <t xml:space="preserve">роль, пользователь, GRANT, REVOKE, матрица прав, проверка</t>
         </is>
       </c>
     </row>
@@ -367,7 +367,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 5. Резервное копирование</t>
+          <t xml:space="preserve">Резервное копирование MySQL</t>
         </is>
       </c>
       <c r="D12" s="6">
@@ -375,12 +375,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Копия нужна не для отчёта, а для восстановления в срок. Разбираются виды копий, расписание, хранение и проверка пригодности копии к восстановлению.</t>
+          <t xml:space="preserve">Копия MySQL нужна для восстановления в срок. Разбираются mysqldump, phpMyAdmin Export, binary logs, расписание и проверка копии.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">полная копия, дифференциальная копия, инкремент, расписание, хранение, проверка копии</t>
+          <t xml:space="preserve">mysqldump, phpMyAdmin, binary log, RPO, RTO, проверка копии</t>
         </is>
       </c>
     </row>
@@ -397,7 +397,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 6. Восстановление</t>
+          <t xml:space="preserve">Восстановление и журналы MySQL</t>
         </is>
       </c>
       <c r="D13" s="6">
@@ -405,16 +405,16 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Восстановление возвращает базу к нужному моменту, а не просто к последней копии. Разбираются полное и точечное восстановление и порядок применения журналов.</t>
+          <t xml:space="preserve">Восстановление MySQL возвращает базу к нужному моменту с помощью дампа и binary log. Разбираются импорт, mysqlbinlog, проверка целостности и порядок действий.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">журнал, целостность, точка отказа, порядок применения, проверка данных</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
+          <t xml:space="preserve">mysql, mysqlbinlog, point-in-time, импорт, целостность, проверка</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">9-10</t>
@@ -427,7 +427,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 3. Резервное копирование; Восстановление</t>
+          <t xml:space="preserve">Резервное копирование и восстановление</t>
         </is>
       </c>
       <c r="D14" s="6">
@@ -435,12 +435,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты делают полную и инкрементную копию учебной базы и восстанавливают её на чистом месте. Сдают скрипты копирования и протокол восстановления с проверкой данных.</t>
+          <t xml:space="preserve">Делают дамп mysqldump и экспорт phpMyAdmin, восстанавливают базу и проверяют binary log. Сдают скрипты и протокол сверки.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">полная копия, инкремент, точка восстановления, проверка данных, протокол, чистое место</t>
+          <t xml:space="preserve">mysqldump, phpMyAdmin, восстановление, binary log, сверка, протокол</t>
         </is>
       </c>
     </row>
@@ -457,7 +457,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 7. Репликация</t>
+          <t xml:space="preserve">Репликация MySQL</t>
         </is>
       </c>
       <c r="D15" s="6">
@@ -465,12 +465,12 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Репликация держит копии базы на нескольких узлах и распределяет чтение. Разбираются ведущий и ведомый узлы, отставание и конфликты записи.</t>
+          <t xml:space="preserve">Репликация MySQL держит копию на втором узле и распределяет чтение. Разбираются source/replica, binary log, отставание и переключение.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ведущий узел, ведомый узел, отставание, конфликт записи, журнал изменений, переключение</t>
+          <t xml:space="preserve">репликация, source, replica, binary log, лаг, failover</t>
         </is>
       </c>
     </row>
@@ -487,7 +487,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 8. Индексы и производительность</t>
+          <t xml:space="preserve">Индексы и производительность InnoDB</t>
         </is>
       </c>
       <c r="D16" s="6">
@@ -495,12 +495,12 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Индекс ускоряет чтение и замедляет запись, поэтому его строят под конкретный запрос. Разбираются виды индексов, селективность и цена поддержки.</t>
+          <t xml:space="preserve">Индекс InnoDB ускоряет чтение и замедляет запись. Разбираются B-tree, составной индекс, селективность, покрывающий и частичный индекс.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">B-дерево, порядок столбцов, селективность, покрытие запроса, стоимость записи, статистика</t>
+          <t xml:space="preserve">B-tree, составной индекс, селективность, покрывающий индекс, SHOW INDEX, стоимость записи</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 9. Оптимизация запросов</t>
+          <t xml:space="preserve">Оптимизация запросов MySQL</t>
         </is>
       </c>
       <c r="D17" s="6">
@@ -525,16 +525,16 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Медленный запрос обычно вызван лишним сканированием, плохим соединением или недостатком статистики. Разбирается чтение плана и порядок исправления.</t>
+          <t xml:space="preserve">Медленный запрос MySQL лечится по EXPLAIN и статистике. Разбираются типы соединений, сканирования, сортировки и порядок оптимизации.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">план выполнения, соединение, сканирование, статистика, подзапрос, время отклика</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="60" customHeight="1">
+          <t xml:space="preserve">EXPLAIN, JOIN, сканирование, статистика, ANALYZE TABLE, время отклика</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">14-15</t>
@@ -547,7 +547,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 4. Индексы; Оптимизация запроса</t>
+          <t xml:space="preserve">Индексы и оптимизация</t>
         </is>
       </c>
       <c r="D18" s="6">
@@ -555,16 +555,16 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты добавляют индексы к учебной базе и сравнивают планы запросов до и после. Сдают SQL-скрипты индексов и замеры времени выполнения.</t>
+          <t xml:space="preserve">Создают большую таблицу, сравнивают EXPLAIN до и после индексов, добавляют составной и покрывающий индекс. Сдают планы и замеры.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">план запроса, полное сканирование, селективность, время выполнения, замер, составной ключ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="60" customHeight="1">
+          <t xml:space="preserve">EXPLAIN, индекс, селективность, покрывающий индекс, ANALYZE TABLE, замер</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
@@ -577,7 +577,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 10. Транзакции и блокировки</t>
+          <t xml:space="preserve">Транзакции и блокировки InnoDB</t>
         </is>
       </c>
       <c r="D19" s="6">
@@ -585,16 +585,16 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Транзакции удерживают данные согласованными, а блокировки решают, кто и когда меняет строку. Разбираются уровни изоляции, взаимные блокировки и откат.</t>
+          <t xml:space="preserve">Транзакции InnoDB удерживают согласованность, а блокировки решают, кто меняет строку. Разбираются уровни изоляции, deadlock и долгие транзакции.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">уровень изоляции, взаимная блокировка, ожидание, откат, долгая транзакция, фиксация</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="60" customHeight="1">
+          <t xml:space="preserve">InnoDB, транзакция, изоляция, deadlock, блокировка, performance_schema</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
@@ -607,7 +607,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 5. Транзакции</t>
+          <t xml:space="preserve">Транзакции</t>
         </is>
       </c>
       <c r="D20" s="6">
@@ -615,12 +615,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты проверяют свойства транзакций на учебной базе: фиксацию, откат и изоляцию параллельных изменений. Сдают SQL-скрипты сценариев и таблицу наблюдений.</t>
+          <t xml:space="preserve">Проверяют транзакции и блокировки InnoDB в двух сессиях, вызывают deadlock и читают performance_schema. Сдают наблюдения.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">фиксация, откат, уровень изоляции, параллельная сессия, ACID, блокировка</t>
+          <t xml:space="preserve">START TRANSACTION, COMMIT, ROLLBACK, изоляция, deadlock, performance_schema</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 11. Импорт и экспорт</t>
+          <t xml:space="preserve">Импорт и экспорт данных</t>
         </is>
       </c>
       <c r="D21" s="6">
@@ -645,12 +645,12 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обмен данными требует договорённости о формате, кодировке и правилах ошибок. Разбираются CSV и JSON, пакетная загрузка и проверка целостности.</t>
+          <t xml:space="preserve">Обмен данными MySQL требует формата, кодировки и правил ошибок. Разбираются CSV, JSON, LOAD DATA, phpMyAdmin Import и проверка строк.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSV, JSON, кодировка, пакетная загрузка, ошибка строки, целостность</t>
+          <t xml:space="preserve">CSV, JSON, LOAD DATA, phpMyAdmin, utf8mb4, сверка строк</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 6. Импорт JSON</t>
+          <t xml:space="preserve">Импорт JSON</t>
         </is>
       </c>
       <c r="D22" s="6">
@@ -675,12 +675,12 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты загружают данные из JSON в таблицы учебной базы и проверяют результат запросами. Сдают скрипт импорта и отчёт о числе загруженных строк.</t>
+          <t xml:space="preserve">Загружают JSON в MySQL через phpMyAdmin и .NET, проверяют utf8mb4, типы и связи. Сдают скрипт и отчёт о строках.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">разбор структуры, тип данных, проверка строк, скрипт, кодировка, связь таблиц</t>
+          <t xml:space="preserve">JSON, phpMyAdmin, utf8mb4, MySqlConnector, проверка, связи</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 7. Экспорт</t>
+          <t xml:space="preserve">Экспорт</t>
         </is>
       </c>
       <c r="D23" s="6">
@@ -705,12 +705,12 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты выгружают данные учебной базы в файл для обмена и проверяют выгрузку обратной загрузкой. Сдают скрипт экспорта и отчёт о сверке строк.</t>
+          <t xml:space="preserve">Выгружают данные MySQL в CSV и JSON, проверяют кодировку и обратную загрузку. Сдают скрипты и сверку.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">формат обмена, CSV, кодировка, сверка, выборка, файл</t>
+          <t xml:space="preserve">CSV, JSON, экспорт, utf8mb4, сверка, файл</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 12. Автоматизация скриптов</t>
+          <t xml:space="preserve">Автоматизация на C# и .NET SDK 10</t>
         </is>
       </c>
       <c r="D24" s="6">
@@ -735,12 +735,12 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Автоматизация убирает ручные шаги из обслуживания базы и делает их повторяемыми. Разбираются параметры скрипта, журналирование и безопасный повторный запуск.</t>
+          <t xml:space="preserve">Автоматизация на C# и .NET SDK 10 делает обслуживание MySQL повторяемым. Разбираются консольное приложение, MySqlConnector, аргументы, журнал и коды возврата.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">параметр, журнал, код возврата, повторный запуск, обработка ошибок, расписание</t>
+          <t xml:space="preserve">.NET SDK 10, C#, MySqlConnector, консольное приложение, журнал, код возврата</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 8. Скрипт автоматизации</t>
+          <t xml:space="preserve">Консольное приложение обслуживания</t>
         </is>
       </c>
       <c r="D25" s="6">
@@ -765,12 +765,12 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты пишут скрипт, который создаёт таблицы, загружает данные и делает копию без ручных шагов. Сдают скрипт с проверкой запуска на чистой базе.</t>
+          <t xml:space="preserve">Пишут консольное приложение .NET SDK 10 для обслуживания MySQL: дамп, проверка, журнал и коды возврата. Запускают дважды.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">идемпотентность, схема, загрузка данных, повторный запуск, проверка, командный файл</t>
+          <t xml:space="preserve">.NET SDK 10, C#, MySqlConnector, дамп, журнал, идемпотентность</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 13. Планировщик заданий</t>
+          <t xml:space="preserve">Планировщик заданий и события MySQL</t>
         </is>
       </c>
       <c r="D26" s="6">
@@ -795,16 +795,16 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Планировщик запускает обслуживание базы без участия человека. Разбираются расписание, права запуска, журнал и обработка сбоя задания.</t>
+          <t xml:space="preserve">Планировщик Windows и события MySQL запускают обслуживание без человека. Разбираются Task Scheduler, MySQL Event Scheduler, права и журнал.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">расписание, задание, права запуска, журнал, сбой, учётная запись службы</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="60" customHeight="1">
+          <t xml:space="preserve">Планировщик Windows, Task Scheduler, MySQL Event, расписание, журнал, права</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="45" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">24</t>
@@ -817,7 +817,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 14. Мониторинг</t>
+          <t xml:space="preserve">Мониторинг MySQL и приложение WinForms</t>
         </is>
       </c>
       <c r="D27" s="6">
@@ -825,16 +825,16 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мониторинг отвечает, что с базой сейчас и что изменится через неделю. Разбираются метрики, пороги оповещений и разбор инцидента по данным наблюдения.</t>
+          <t xml:space="preserve">Мониторинг MySQL отвечает, что с базой сейчас. Разбираются performance_schema, статусы, долгие запросы, блокировки и приложение WinForms.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">метрика, порог, оповещение, журнал, нагрузка, инцидент</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="60" customHeight="1">
+          <t xml:space="preserve">performance_schema, SHOW STATUS, метрика, порог, WinForms, мониторинг</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">25-26</t>
@@ -847,7 +847,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 9. Планировщик; Мониторинг</t>
+          <t xml:space="preserve">Планировщик и мониторинг</t>
         </is>
       </c>
       <c r="D28" s="6">
@@ -855,12 +855,12 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты ставят скрипт обслуживания в планировщик и настраивают сбор метрик учебной базы. Сдают задание планировщика, скрипт метрик и отчёт наблюдений.</t>
+          <t xml:space="preserve">Ставят приложение обслуживания в Планировщик Windows, собирают метрики MySQL и выводят их в WinForms. Сдают задание, метрики и отчёт.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">расписание, метрика, журнал запуска, соединение, наблюдение, порог</t>
+          <t xml:space="preserve">Task Scheduler, performance_schema, метрика, WinForms, журнал, порог</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 15. Аудит</t>
+          <t xml:space="preserve">Аудит MySQL</t>
         </is>
       </c>
       <c r="D29" s="6">
@@ -885,16 +885,16 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Аудит фиксирует, кто и что сделал с данными, и помогает разобрать инцидент. Разбираются события, хранение журнала и разграничение доступа к нему.</t>
+          <t xml:space="preserve">Аудит MySQL фиксирует, кто и что сделал. Разбираются general log, триггерная таблица, хранение и защита журнала.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">событие, журнал, политика, хранение, разбор инцидента, подотчётность</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="45" customHeight="1">
+          <t xml:space="preserve">general log, аудит, триггер, журнал, хранение, подотчётность</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">28</t>
@@ -907,7 +907,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 16. Безопасность</t>
+          <t xml:space="preserve">Безопасность MySQL и .NET</t>
         </is>
       </c>
       <c r="D30" s="6">
@@ -915,16 +915,16 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Безопасность базы строится на минимальных правах, защите секретов и контроле доступа к копиям. Разбираются типовые атаки и меры защиты данных.</t>
+          <t xml:space="preserve">Безопасность MySQL и .NET строится на минимальных правах, защите строки подключения и проверке ввода. Разбираются SQL-инъекции, секреты и доступ к дампам.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">привилегия, строка подключения, секрет, шифрование, инъекция, доступ к копиям</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="60" customHeight="1">
+          <t xml:space="preserve">привилегия, строка подключения, секрет, SQL-инъекция, параметризованный запрос, дамп</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="45" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">29-30</t>
@@ -937,7 +937,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 10. Аудит; Безопасность</t>
+          <t xml:space="preserve">Аудит и безопасность</t>
         </is>
       </c>
       <c r="D31" s="6">
@@ -945,12 +945,12 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты включают аудит действий в учебной базе и проверяют защиту доступа, секретов и копий. Сдают настройки аудита, выгрузку событий и список рисков.</t>
+          <t xml:space="preserve">Включают аудит MySQL, создают триггерную таблицу и проверяют права и секреты. Сдают события, матрицу доступа и риски.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">событие, журнал доступа, секрет, права, риск, мера защиты</t>
+          <t xml:space="preserve">general log, триггер, аудит, привилегия, секрет, риск</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 17. Миграции</t>
+          <t xml:space="preserve">Миграции схемы MySQL</t>
         </is>
       </c>
       <c r="D32" s="6">
@@ -975,12 +975,12 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Миграция меняет схему на работающей базе без остановки и потери данных. Разбираются версии, прямой и обратный скрипт, проверка и порядок выпуска.</t>
+          <t xml:space="preserve">Миграция MySQL меняет схему без потери данных. Разбираются версии, ALTER TABLE, backfill, обратный скрипт и проверка на копии.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">версия, обратный скрипт, совместимость, проверка, выпуск, окно обслуживания</t>
+          <t xml:space="preserve">миграция, schema_version, ALTER TABLE, backfill, rollback, проверка</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 11. Миграция</t>
+          <t xml:space="preserve">Миграция</t>
         </is>
       </c>
       <c r="D33" s="6">
@@ -1005,12 +1005,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты переносят учебную базу на новую версию схемы с сохранением данных. Сдают скрипты миграции и отката и отчёт о проверке данных.</t>
+          <t xml:space="preserve">Меняют схему MySQL через ALTER TABLE, заполняют новое поле и проверяют обратный скрипт. Сдают миграцию и откат.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">версия схемы, откат, перенос данных, проверка, скрипт, совместимость</t>
+          <t xml:space="preserve">ALTER TABLE, schema_version, backfill, rollback, миграция, проверка</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 12. Итоговая БД</t>
+          <t xml:space="preserve">Итоговая база и .NET-приложение</t>
         </is>
       </c>
       <c r="D34" s="6">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты собирают учебную базу целиком: схема, роли, индексы, копия и скрипт обслуживания. Сдают базу и комплект скриптов с протоколом проверки.</t>
+          <t xml:space="preserve">Собирают итоговую базу MySQL и .NET-приложение: схема, роли, индексы, дамп, обслуживание. Сдают комплект и протокол.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">схема, ограничение, роль, индекс, копия, чек-лист</t>
+          <t xml:space="preserve">MySQL, схема, роль, индекс, дамп, .NET</t>
         </is>
       </c>
     </row>

--- a/docs/4/db-automation/Учебный_план_Управление_и_автоматизация_баз_данных.xlsx
+++ b/docs/4/db-automation/Учебный_план_Управление_и_автоматизация_баз_данных.xlsx
@@ -187,7 +187,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Управление и автоматизация БД</t>
+          <t xml:space="preserve">Лекция 1. Управление и автоматизация БД</t>
         </is>
       </c>
       <c r="D6" s="6">
@@ -217,7 +217,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Архитектура MySQL и InnoDB</t>
+          <t xml:space="preserve">Лекция 2. Архитектура MySQL и InnoDB</t>
         </is>
       </c>
       <c r="D7" s="6">
@@ -247,7 +247,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">XAMPP, MySQL и подключение из .NET</t>
+          <t xml:space="preserve">Лекция 3. XAMPP, MySQL и подключение из .NET</t>
         </is>
       </c>
       <c r="D8" s="6">
@@ -277,7 +277,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Запуск XAMPP, база utf8mb4, подключение из .NET</t>
+          <t xml:space="preserve">Практика 1. Запуск XAMPP, база utf8mb4, подключение из .NET</t>
         </is>
       </c>
       <c r="D9" s="6">
@@ -307,7 +307,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пользователи и роли MySQL</t>
+          <t xml:space="preserve">Лекция 4. Пользователи и роли MySQL</t>
         </is>
       </c>
       <c r="D10" s="6">
@@ -337,7 +337,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Роли и доступ в MySQL</t>
+          <t xml:space="preserve">Практика 2. Роли и доступ в MySQL</t>
         </is>
       </c>
       <c r="D11" s="6">
@@ -367,7 +367,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Резервное копирование MySQL</t>
+          <t xml:space="preserve">Лекция 5. Резервное копирование MySQL</t>
         </is>
       </c>
       <c r="D12" s="6">
@@ -397,7 +397,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Восстановление и журналы MySQL</t>
+          <t xml:space="preserve">Лекция 6. Восстановление и журналы MySQL</t>
         </is>
       </c>
       <c r="D13" s="6">
@@ -427,7 +427,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Резервное копирование и восстановление</t>
+          <t xml:space="preserve">Практика 3. Резервное копирование и восстановление</t>
         </is>
       </c>
       <c r="D14" s="6">
@@ -457,7 +457,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Репликация MySQL</t>
+          <t xml:space="preserve">Лекция 7. Репликация MySQL</t>
         </is>
       </c>
       <c r="D15" s="6">
@@ -487,7 +487,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Индексы и производительность InnoDB</t>
+          <t xml:space="preserve">Лекция 8. Индексы и производительность InnoDB</t>
         </is>
       </c>
       <c r="D16" s="6">
@@ -517,7 +517,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оптимизация запросов MySQL</t>
+          <t xml:space="preserve">Лекция 9. Оптимизация запросов MySQL</t>
         </is>
       </c>
       <c r="D17" s="6">
@@ -547,7 +547,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Индексы и оптимизация</t>
+          <t xml:space="preserve">Практика 4. Индексы и оптимизация</t>
         </is>
       </c>
       <c r="D18" s="6">
@@ -577,7 +577,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Транзакции и блокировки InnoDB</t>
+          <t xml:space="preserve">Лекция 10. Транзакции и блокировки InnoDB</t>
         </is>
       </c>
       <c r="D19" s="6">
@@ -607,7 +607,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Транзакции</t>
+          <t xml:space="preserve">Практика 5. Транзакции</t>
         </is>
       </c>
       <c r="D20" s="6">
@@ -637,7 +637,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Импорт и экспорт данных</t>
+          <t xml:space="preserve">Лекция 11. Импорт и экспорт данных</t>
         </is>
       </c>
       <c r="D21" s="6">
@@ -667,7 +667,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Импорт JSON</t>
+          <t xml:space="preserve">Практика 6. Импорт JSON</t>
         </is>
       </c>
       <c r="D22" s="6">
@@ -697,7 +697,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Экспорт</t>
+          <t xml:space="preserve">Практика 7. Экспорт</t>
         </is>
       </c>
       <c r="D23" s="6">
@@ -727,7 +727,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Автоматизация на C# и .NET SDK 10</t>
+          <t xml:space="preserve">Лекция 12. Автоматизация на C# и .NET SDK 10</t>
         </is>
       </c>
       <c r="D24" s="6">
@@ -757,7 +757,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Консольное приложение обслуживания</t>
+          <t xml:space="preserve">Практика 8. Консольное приложение обслуживания</t>
         </is>
       </c>
       <c r="D25" s="6">
@@ -787,7 +787,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Планировщик заданий и события MySQL</t>
+          <t xml:space="preserve">Лекция 13. Планировщик заданий и события MySQL</t>
         </is>
       </c>
       <c r="D26" s="6">
@@ -817,7 +817,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мониторинг MySQL и приложение WinForms</t>
+          <t xml:space="preserve">Лекция 14. Мониторинг MySQL и приложение WinForms</t>
         </is>
       </c>
       <c r="D27" s="6">
@@ -847,7 +847,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Планировщик и мониторинг</t>
+          <t xml:space="preserve">Практика 9. Планировщик и мониторинг</t>
         </is>
       </c>
       <c r="D28" s="6">
@@ -877,7 +877,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Аудит MySQL</t>
+          <t xml:space="preserve">Лекция 15. Аудит MySQL</t>
         </is>
       </c>
       <c r="D29" s="6">
@@ -907,7 +907,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Безопасность MySQL и .NET</t>
+          <t xml:space="preserve">Лекция 16. Безопасность MySQL и .NET</t>
         </is>
       </c>
       <c r="D30" s="6">
@@ -937,7 +937,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Аудит и безопасность</t>
+          <t xml:space="preserve">Практика 10. Аудит и безопасность</t>
         </is>
       </c>
       <c r="D31" s="6">
@@ -967,7 +967,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Миграции схемы MySQL</t>
+          <t xml:space="preserve">Лекция 17. Миграции схемы MySQL</t>
         </is>
       </c>
       <c r="D32" s="6">
@@ -997,7 +997,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Миграция</t>
+          <t xml:space="preserve">Практика 11. Миграция</t>
         </is>
       </c>
       <c r="D33" s="6">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Итоговая база и .NET-приложение</t>
+          <t xml:space="preserve">Практика 12. Итоговая база и .NET-приложение</t>
         </is>
       </c>
       <c r="D34" s="6">

--- a/docs/4/db-automation/Учебный_план_Управление_и_автоматизация_баз_данных.xlsx
+++ b/docs/4/db-automation/Учебный_план_Управление_и_автоматизация_баз_данных.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Запускают MySQL в XAMPP, создают базу dean в phpMyAdmin с utf8mb4, подключаются из консольного приложения .NET SDK 10 и сдают протокол.</t>
+          <t xml:space="preserve">Вы запускаете MySQL в XAMPP, создаёте базу dean в phpMyAdmin с utf8mb4, подключаетесь из консольного приложения .NET SDK 10 и сдаёте протокол.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -345,7 +345,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Создают пользователей и роли MySQL, выдают минимальные права и проверяют доступ из phpMyAdmin и .NET. Сдают SQL-скрипт и матрицу прав.</t>
+          <t xml:space="preserve">Вы создаёте пользователей и роли MySQL, выдаёте минимальные права и проверяете доступ из phpMyAdmin и .NET. Сдаёте SQL-скрипт и матрицу прав.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -435,7 +435,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Делают дамп mysqldump и экспорт phpMyAdmin, восстанавливают базу и проверяют binary log. Сдают скрипты и протокол сверки.</t>
+          <t xml:space="preserve">Вы делаете дамп mysqldump и экспорт phpMyAdmin, восстанавливаете базу и проверяете binary log. Сдаёте скрипты и протокол сверки.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Создают большую таблицу, сравнивают EXPLAIN до и после индексов, добавляют составной и покрывающий индекс. Сдают планы и замеры.</t>
+          <t xml:space="preserve">Вы создаёте большую таблицу, сравниваете EXPLAIN до и после индексов, добавляете составной и покрывающий индекс. Сдаёте планы и замеры.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Проверяют транзакции и блокировки InnoDB в двух сессиях, вызывают deadlock и читают performance_schema. Сдают наблюдения.</t>
+          <t xml:space="preserve">Вы проверяете транзакции и блокировки InnoDB в двух сессиях, вызываете deadlock и читаете performance_schema. Сдаёте наблюдения.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Загружают JSON в MySQL через phpMyAdmin и .NET, проверяют utf8mb4, типы и связи. Сдают скрипт и отчёт о строках.</t>
+          <t xml:space="preserve">Вы загружаете JSON в MySQL через phpMyAdmin и .NET, проверяете utf8mb4, типы и связи. Сдаёте скрипт и отчёт о строках.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Выгружают данные MySQL в CSV и JSON, проверяют кодировку и обратную загрузку. Сдают скрипты и сверку.</t>
+          <t xml:space="preserve">Вы выгружаете данные MySQL в CSV и JSON, проверяете кодировку и обратную загрузку. Сдаёте скрипты и сверку.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пишут консольное приложение .NET SDK 10 для обслуживания MySQL: дамп, проверка, журнал и коды возврата. Запускают дважды.</t>
+          <t xml:space="preserve">Вы пишете консольное приложение .NET SDK 10 для обслуживания MySQL: дамп, проверка, журнал и коды возврата. Запускаете дважды.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ставят приложение обслуживания в Планировщик Windows, собирают метрики MySQL и выводят их в WinForms. Сдают задание, метрики и отчёт.</t>
+          <t xml:space="preserve">Вы ставите приложение обслуживания в Планировщик Windows, собираете метрики MySQL и выводите их в WinForms. Сдаёте задание, метрики и отчёт.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Включают аудит MySQL, создают триггерную таблицу и проверяют права и секреты. Сдают события, матрицу доступа и риски.</t>
+          <t xml:space="preserve">Вы включаете аудит MySQL, создаёте триггерную таблицу и проверяете права и секреты. Сдаёте события, матрицу доступа и риски.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Меняют схему MySQL через ALTER TABLE, заполняют новое поле и проверяют обратный скрипт. Сдают миграцию и откат.</t>
+          <t xml:space="preserve">Вы меняете схему MySQL через ALTER TABLE, заполняете новое поле и проверяете обратный скрипт. Сдаёте миграцию и откат.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Собирают итоговую базу MySQL и .NET-приложение: схема, роли, индексы, дамп, обслуживание. Сдают комплект и протокол.</t>
+          <t xml:space="preserve">Вы собираете итоговую базу MySQL и .NET-приложение: схема, роли, индексы, дамп, обслуживание. Сдаёте комплект и протокол.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
